--- a/Сайт-Куницкого-план.xlsx
+++ b/Сайт-Куницкого-план.xlsx
@@ -548,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -581,7 +581,7 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Жёлтые ячейки — то, что заполняете вы. Даты пересчитаются сами.</t>
+          <t>Жёлтые ячейки — то, что заполняете вы. Даты пересчитаются сами. День 0 — день, когда пришли данные от заказчика.</t>
         </is>
       </c>
     </row>
@@ -643,24 +643,24 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>1. Техническое задание</t>
+          <t>1. Уже сделано</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>Собрать требования и цели сайта</t>
+          <t>Каркас сайта и 3D-сцена первого экрана</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Заказчик</t>
+          <t>Разработка</t>
         </is>
       </c>
       <c r="E5" s="9" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5" s="10">
         <f>$B$2+E5</f>
@@ -672,14 +672,10 @@
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>В работе</t>
-        </is>
-      </c>
-      <c r="J5" s="8" t="inlineStr">
-        <is>
-          <t>Кому показываем, что должно произойти после просмотра</t>
-        </is>
-      </c>
+          <t>Готово</t>
+        </is>
+      </c>
+      <c r="J5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
@@ -687,24 +683,24 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>1. Техническое задание</t>
+          <t>1. Уже сделано</t>
         </is>
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>Утвердить структуру разделов</t>
+          <t>Все семь разделов со скролл-анимациями</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Заказчик</t>
+          <t>Разработка</t>
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" s="14">
         <f>$B$2+E6</f>
@@ -716,14 +712,10 @@
       </c>
       <c r="I6" s="11" t="inlineStr">
         <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="J6" s="13" t="inlineStr">
-        <is>
-          <t>Текущая структура — 7 разделов, можно взять за основу</t>
-        </is>
-      </c>
+          <t>Готово</t>
+        </is>
+      </c>
+      <c r="J6" s="13" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
@@ -731,24 +723,24 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>1. Техническое задание</t>
+          <t>1. Уже сделано</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>Согласовать ТЗ с Куницким Е.А.</t>
+          <t>Четыре языка, включая арабский</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Заказчик</t>
+          <t>Разработка</t>
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G7" s="14">
         <f>$B$2+E7</f>
@@ -760,58 +752,50 @@
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="J7" s="13" t="inlineStr">
-        <is>
-          <t>Ключевая точка: без этого дизайн будет переделываться</t>
-        </is>
-      </c>
+          <t>Готово</t>
+        </is>
+      </c>
+      <c r="J7" s="13" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="n">
+      <c r="A8" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>2. Дизайн</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Прототип первого экрана и ключевых секций</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>Дизайнер</t>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>1. Уже сделано</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>Вёрстка под телефон</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>Разработка</t>
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="G8" s="10">
+        <v>1</v>
+      </c>
+      <c r="G8" s="14">
         <f>$B$2+E8</f>
         <v/>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="14">
         <f>G8+F8-1</f>
         <v/>
       </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t>Прототип обсуждать дешевле, чем готовый макет</t>
-        </is>
-      </c>
+      <c r="I8" s="11" t="inlineStr">
+        <is>
+          <t>Готово</t>
+        </is>
+      </c>
+      <c r="J8" s="13" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
@@ -819,24 +803,24 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>2. Дизайн</t>
+          <t>1. Уже сделано</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>Макеты: десктоп и телефон</t>
+          <t>Визуализации семи объектов</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Дизайнер</t>
+          <t>Разработка</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G9" s="14">
         <f>$B$2+E9</f>
@@ -848,14 +832,10 @@
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="J9" s="13" t="inlineStr">
-        <is>
-          <t>Телефон — основной сценарий просмотра</t>
-        </is>
-      </c>
+          <t>Готово</t>
+        </is>
+      </c>
+      <c r="J9" s="13" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="n">
@@ -863,24 +843,24 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>2. Дизайн</t>
+          <t>1. Уже сделано</t>
         </is>
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>Правки по итогам показа</t>
+          <t>Карта присутствия</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Дизайнер</t>
+          <t>Разработка</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G10" s="14">
         <f>$B$2+E10</f>
@@ -892,7 +872,7 @@
       </c>
       <c r="I10" s="11" t="inlineStr">
         <is>
-          <t>Не начато</t>
+          <t>Готово</t>
         </is>
       </c>
       <c r="J10" s="13" t="inlineStr"/>
@@ -903,24 +883,24 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>2. Дизайн</t>
+          <t>1. Уже сделано</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>Утверждение дизайна</t>
+          <t>Разделы «Масштаб» и «Признание»</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Заказчик</t>
+          <t>Разработка</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" s="14">
         <f>$B$2+E11</f>
@@ -932,56 +912,52 @@
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="J11" s="13" t="inlineStr">
-        <is>
-          <t>После этой точки правки макета стоят дороже</t>
-        </is>
-      </c>
+          <t>Готово</t>
+        </is>
+      </c>
+      <c r="J11" s="13" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="n">
+      <c r="A12" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>3. Контент</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Биография и карьерный путь</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>Куницкий Е.А.</t>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>1. Уже сделано</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Превью ссылки для мессенджеров</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>Разработка</t>
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="G12" s="10">
+        <v>1</v>
+      </c>
+      <c r="G12" s="14">
         <f>$B$2+E12</f>
         <v/>
       </c>
-      <c r="H12" s="10">
+      <c r="H12" s="14">
         <f>G12+F12-1</f>
         <v/>
       </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>Ждёт данных</t>
-        </is>
-      </c>
-      <c r="J12" s="8" t="inlineStr">
-        <is>
-          <t>В открытых источниках нет — только от него</t>
+      <c r="I12" s="11" t="inlineStr">
+        <is>
+          <t>Готово</t>
+        </is>
+      </c>
+      <c r="J12" s="13" t="inlineStr">
+        <is>
+          <t>Картинка, заголовок и описание при пересылке</t>
         </is>
       </c>
     </row>
@@ -991,24 +967,24 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>3. Контент</t>
+          <t>1. Уже сделано</t>
         </is>
       </c>
       <c r="C13" s="13" t="inlineStr">
         <is>
-          <t>Портретная съёмка</t>
+          <t>Разметка для поисковиков</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Заказчик</t>
+          <t>Разработка</t>
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G13" s="14">
         <f>$B$2+E13</f>
@@ -1020,12 +996,12 @@
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>Ждёт данных</t>
+          <t>Готово</t>
         </is>
       </c>
       <c r="J13" s="13" t="inlineStr">
         <is>
-          <t>Сейчас вместо портрета чертёжная рамка</t>
+          <t>Как ссылка выглядит в выдаче</t>
         </is>
       </c>
     </row>
@@ -1035,24 +1011,24 @@
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>3. Контент</t>
+          <t>1. Уже сделано</t>
         </is>
       </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
-          <t>Цитаты и тезисы</t>
+          <t>robots.txt и карта сайта</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>Куницкий Е.А.</t>
+          <t>Разработка</t>
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14" s="14">
         <f>$B$2+E14</f>
@@ -1067,11 +1043,7 @@
           <t>Готово</t>
         </is>
       </c>
-      <c r="J14" s="13" t="inlineStr">
-        <is>
-          <t>Есть: «Мы строим там, где никто не строит»</t>
-        </is>
-      </c>
+      <c r="J14" s="13" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="11" t="n">
@@ -1079,24 +1051,24 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>3. Контент</t>
+          <t>1. Уже сделано</t>
         </is>
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>Выступления и публикации</t>
+          <t>Политика конфиденциальности</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Заказчик</t>
+          <t>Разработка</t>
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G15" s="14">
         <f>$B$2+E15</f>
@@ -1108,12 +1080,12 @@
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>Ждёт данных</t>
+          <t>Готово</t>
         </is>
       </c>
       <c r="J15" s="13" t="inlineStr">
         <is>
-          <t>Сейчас одна запись</t>
+          <t>Черновик; нужен просмотр юриста</t>
         </is>
       </c>
     </row>
@@ -1123,24 +1095,24 @@
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>3. Контент</t>
+          <t>1. Уже сделано</t>
         </is>
       </c>
       <c r="C16" s="13" t="inlineStr">
         <is>
-          <t>Подтвердить статус награды Минстроя</t>
+          <t>Подстройка качества под слабые устройства</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>Заказчик</t>
+          <t>Разработка</t>
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G16" s="14">
         <f>$B$2+E16</f>
@@ -1152,56 +1124,52 @@
       </c>
       <c r="I16" s="11" t="inlineStr">
         <is>
-          <t>Ждёт данных</t>
-        </is>
-      </c>
-      <c r="J16" s="13" t="inlineStr">
-        <is>
-          <t>Представление к награде или уже вручена — формулировки разные</t>
-        </is>
-      </c>
+          <t>Готово</t>
+        </is>
+      </c>
+      <c r="J16" s="13" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="n">
+      <c r="A17" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>3. Контент</t>
-        </is>
-      </c>
-      <c r="C17" s="13" t="inlineStr">
-        <is>
-          <t>Уточнить название объекта в Мурманске</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>2. Ждём от заказчика</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Ссылки на мессенджеры</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>Заказчик</t>
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G17" s="14">
+      <c r="G17" s="10">
         <f>$B$2+E17</f>
         <v/>
       </c>
-      <c r="H17" s="14">
+      <c r="H17" s="10">
         <f>G17+F17-1</f>
         <v/>
       </c>
-      <c r="I17" s="11" t="inlineStr">
+      <c r="I17" s="6" t="inlineStr">
         <is>
           <t>Ждёт данных</t>
         </is>
       </c>
-      <c r="J17" s="13" t="inlineStr">
-        <is>
-          <t>«Берег Арктики» или «Квартал в Росляково» — один объект или два</t>
+      <c r="J17" s="8" t="inlineStr">
+        <is>
+          <t>Блокирует главное действие сайта</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1179,12 @@
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>3. Контент</t>
+          <t>2. Ждём от заказчика</t>
         </is>
       </c>
       <c r="C18" s="13" t="inlineStr">
         <is>
-          <t>Ссылки на мессенджеры</t>
+          <t>Портрет</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
@@ -1225,7 +1193,7 @@
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F18" s="9" t="n">
         <v>1</v>
@@ -1245,7 +1213,7 @@
       </c>
       <c r="J18" s="13" t="inlineStr">
         <is>
-          <t>Главное действие сайта; кнопки пока неактивны</t>
+          <t>Файлы загрузить в public/images в репозитории</t>
         </is>
       </c>
     </row>
@@ -1255,24 +1223,24 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>3. Контент</t>
+          <t>2. Ждём от заказчика</t>
         </is>
       </c>
       <c r="C19" s="13" t="inlineStr">
         <is>
-          <t>Проверка переводов носителями</t>
+          <t>Фото с площадок: ВЭФ, ПМЭФ, Сбер</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Подрядчик</t>
+          <t>Заказчик</t>
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G19" s="14">
         <f>$B$2+E19</f>
@@ -1284,56 +1252,56 @@
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>Не начато</t>
+          <t>Ждёт данных</t>
         </is>
       </c>
       <c r="J19" s="13" t="inlineStr">
         <is>
-          <t>EN, китайский, арабский</t>
+          <t>Снимки видел, файлов нет</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="n">
+      <c r="A20" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>4. Разработка</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>Каркас сайта и 3D-сцена первого экрана</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>Разработка</t>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>2. Ждём от заказчика</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>Биография и карьерный путь</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>Куницкий Е.А.</t>
         </is>
       </c>
       <c r="E20" s="9" t="n">
         <v>0</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" s="10">
+        <v>3</v>
+      </c>
+      <c r="G20" s="14">
         <f>$B$2+E20</f>
         <v/>
       </c>
-      <c r="H20" s="10">
+      <c r="H20" s="14">
         <f>G20+F20-1</f>
         <v/>
       </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>Готово</t>
-        </is>
-      </c>
-      <c r="J20" s="8" t="inlineStr">
-        <is>
-          <t>Сделано</t>
+      <c r="I20" s="11" t="inlineStr">
+        <is>
+          <t>Ждёт данных</t>
+        </is>
+      </c>
+      <c r="J20" s="13" t="inlineStr">
+        <is>
+          <t>В открытых источниках ничего нет</t>
         </is>
       </c>
     </row>
@@ -1343,17 +1311,17 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>4. Разработка</t>
+          <t>2. Ждём от заказчика</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>Секции и скролл-анимации</t>
+          <t>Статус награды Минстроя</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Разработка</t>
+          <t>Заказчик</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
@@ -1372,12 +1340,12 @@
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>Готово</t>
+          <t>Ждёт данных</t>
         </is>
       </c>
       <c r="J21" s="13" t="inlineStr">
         <is>
-          <t>Сделано</t>
+          <t>Представление или вручённая награда</t>
         </is>
       </c>
     </row>
@@ -1387,24 +1355,24 @@
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>4. Разработка</t>
+          <t>2. Ждём от заказчика</t>
         </is>
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>Четыре языка, включая арабский</t>
+          <t>Даты и названия выступлений</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>Разработка</t>
+          <t>Заказчик</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" s="14">
         <f>$B$2+E22</f>
@@ -1416,14 +1384,10 @@
       </c>
       <c r="I22" s="11" t="inlineStr">
         <is>
-          <t>Готово</t>
-        </is>
-      </c>
-      <c r="J22" s="13" t="inlineStr">
-        <is>
-          <t>Сделано</t>
-        </is>
-      </c>
+          <t>Ждёт данных</t>
+        </is>
+      </c>
+      <c r="J22" s="13" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="11" t="n">
@@ -1431,17 +1395,17 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>4. Разработка</t>
+          <t>2. Ждём от заказчика</t>
         </is>
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
-          <t>Вёрстка под телефон</t>
+          <t>Название объекта в Мурманске</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Разработка</t>
+          <t>Заказчик</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
@@ -1460,12 +1424,12 @@
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>Готово</t>
+          <t>Ждёт данных</t>
         </is>
       </c>
       <c r="J23" s="13" t="inlineStr">
         <is>
-          <t>Сделано</t>
+          <t>«Берег Арктики» или «Росляково»</t>
         </is>
       </c>
     </row>
@@ -1475,24 +1439,24 @@
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>4. Разработка</t>
+          <t>2. Ждём от заказчика</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
-          <t>Правки по утверждённому дизайну</t>
+          <t>Домен</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>Разработка</t>
+          <t>Заказчик</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G24" s="14">
         <f>$B$2+E24</f>
@@ -1504,56 +1468,52 @@
       </c>
       <c r="I24" s="11" t="inlineStr">
         <is>
+          <t>Ждёт данных</t>
+        </is>
+      </c>
+      <c r="J24" s="13" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>3. Как придут данные</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Подставить портрет и фото площадок</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>Разработка</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="10">
+        <f>$B$2+E25</f>
+        <v/>
+      </c>
+      <c r="H25" s="10">
+        <f>G25+F25-1</f>
+        <v/>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
           <t>Не начато</t>
         </is>
       </c>
-      <c r="J24" s="13" t="inlineStr">
-        <is>
-          <t>Объём зависит от того, насколько дизайн разойдётся с текущим</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="11" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>4. Разработка</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
-        <is>
-          <t>Подключение контента заказчика</t>
-        </is>
-      </c>
-      <c r="D25" s="12" t="inlineStr">
-        <is>
-          <t>Разработка</t>
-        </is>
-      </c>
-      <c r="E25" s="9" t="n">
-        <v>29</v>
-      </c>
-      <c r="F25" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G25" s="14">
-        <f>$B$2+E25</f>
-        <v/>
-      </c>
-      <c r="H25" s="14">
-        <f>G25+F25-1</f>
-        <v/>
-      </c>
-      <c r="I25" s="11" t="inlineStr">
-        <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="J25" s="13" t="inlineStr">
-        <is>
-          <t>Тексты лежат отдельно от вёрстки, подстановка быстрая</t>
+      <c r="J25" s="8" t="inlineStr">
+        <is>
+          <t>Тексты и фото лежат отдельно от вёрстки</t>
         </is>
       </c>
     </row>
@@ -1563,12 +1523,12 @@
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>4. Разработка</t>
+          <t>3. Как придут данные</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>Обратная связь: бот или прямой чат</t>
+          <t>Подставить биографию и выступления</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
@@ -1577,10 +1537,10 @@
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G26" s="14">
         <f>$B$2+E26</f>
@@ -1595,53 +1555,49 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="J26" s="13" t="inlineStr">
-        <is>
-          <t>Решить, что именно, до этого этапа</t>
-        </is>
-      </c>
+      <c r="J26" s="13" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="n">
+      <c r="A27" s="11" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>5. Запуск</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>Выбор и покупка домена</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>Заказчик</t>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>3. Как придут данные</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>Включить кнопки мессенджеров</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>Разработка</t>
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G27" s="10">
+        <v>1</v>
+      </c>
+      <c r="G27" s="14">
         <f>$B$2+E27</f>
         <v/>
       </c>
-      <c r="H27" s="10">
+      <c r="H27" s="14">
         <f>G27+F27-1</f>
         <v/>
       </c>
-      <c r="I27" s="6" t="inlineStr">
+      <c r="I27" s="11" t="inlineStr">
         <is>
           <t>Не начато</t>
         </is>
       </c>
-      <c r="J27" s="8" t="inlineStr">
-        <is>
-          <t>Пока сайт открывается по техническому адресу</t>
+      <c r="J27" s="13" t="inlineStr">
+        <is>
+          <t>Правка одного файла</t>
         </is>
       </c>
     </row>
@@ -1651,12 +1607,12 @@
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>5. Запуск</t>
+          <t>3. Как придут данные</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>Настройка домена и сертификата</t>
+          <t>Уточнить формулировки по награде</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
@@ -1665,7 +1621,7 @@
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>1</v>
@@ -1691,24 +1647,24 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>5. Запуск</t>
+          <t>3. Как придут данные</t>
         </is>
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>Политика конфиденциальности</t>
+          <t>Показ Куницкому Е.А.</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Юрист</t>
+          <t>Заказчик</t>
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G29" s="14">
         <f>$B$2+E29</f>
@@ -1725,7 +1681,7 @@
       </c>
       <c r="J29" s="13" t="inlineStr">
         <is>
-          <t>Нужна, если собираются любые данные посетителей</t>
+          <t>Первый показ на реальном содержании</t>
         </is>
       </c>
     </row>
@@ -1735,12 +1691,12 @@
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>5. Запуск</t>
+          <t>3. Как придут данные</t>
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>Счётчики аналитики</t>
+          <t>Правки по итогам показа</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
@@ -1749,10 +1705,10 @@
         </is>
       </c>
       <c r="E30" s="9" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G30" s="14">
         <f>$B$2+E30</f>
@@ -1769,53 +1725,49 @@
       </c>
       <c r="J30" s="13" t="inlineStr">
         <is>
-          <t>Яндекс.Метрика</t>
+          <t>Запас на замечания</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="n">
+      <c r="A31" s="6" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="12" t="inlineStr">
-        <is>
-          <t>5. Запуск</t>
-        </is>
-      </c>
-      <c r="C31" s="13" t="inlineStr">
-        <is>
-          <t>Проверка на реальных устройствах</t>
-        </is>
-      </c>
-      <c r="D31" s="12" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>4. Запуск</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Настройка домена и сертификата</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>Разработка</t>
         </is>
       </c>
       <c r="E31" s="9" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G31" s="14">
+        <v>1</v>
+      </c>
+      <c r="G31" s="10">
         <f>$B$2+E31</f>
         <v/>
       </c>
-      <c r="H31" s="14">
+      <c r="H31" s="10">
         <f>G31+F31-1</f>
         <v/>
       </c>
-      <c r="I31" s="11" t="inlineStr">
+      <c r="I31" s="6" t="inlineStr">
         <is>
           <t>Не начато</t>
         </is>
       </c>
-      <c r="J31" s="13" t="inlineStr">
-        <is>
-          <t>iPhone, Android, медленный интернет</t>
-        </is>
-      </c>
+      <c r="J31" s="8" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="11" t="n">
@@ -1823,24 +1775,24 @@
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>5. Запуск</t>
+          <t>4. Запуск</t>
         </is>
       </c>
       <c r="C32" s="13" t="inlineStr">
         <is>
-          <t>Показ Куницкому Е.А. и приёмка</t>
+          <t>Счётчик аналитики</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>Заказчик</t>
+          <t>Разработка</t>
         </is>
       </c>
       <c r="E32" s="9" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G32" s="14">
         <f>$B$2+E32</f>
@@ -1863,24 +1815,24 @@
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>5. Запуск</t>
+          <t>4. Запуск</t>
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr">
         <is>
-          <t>Публикация</t>
+          <t>Политику посмотрит юрист</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Разработка</t>
+          <t>Юрист</t>
         </is>
       </c>
       <c r="E33" s="9" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" s="14">
         <f>$B$2+E33</f>
@@ -1895,47 +1847,55 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="J33" s="13" t="inlineStr"/>
+      <c r="J33" s="13" t="inlineStr">
+        <is>
+          <t>Черновик готов</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="n">
+      <c r="A34" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>6. После запуска</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>Наблюдение и мелкие правки</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>4. Запуск</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>Проверка на реальных устройствах</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
         <is>
           <t>Разработка</t>
         </is>
       </c>
       <c r="E34" s="9" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="G34" s="10">
+        <v>1</v>
+      </c>
+      <c r="G34" s="14">
         <f>$B$2+E34</f>
         <v/>
       </c>
-      <c r="H34" s="10">
+      <c r="H34" s="14">
         <f>G34+F34-1</f>
         <v/>
       </c>
-      <c r="I34" s="6" t="inlineStr">
+      <c r="I34" s="11" t="inlineStr">
         <is>
           <t>Не начато</t>
         </is>
       </c>
-      <c r="J34" s="8" t="inlineStr"/>
+      <c r="J34" s="13" t="inlineStr">
+        <is>
+          <t>iPhone, Android, медленный интернет</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="n">
@@ -1943,12 +1903,12 @@
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>6. После запуска</t>
+          <t>4. Запуск</t>
         </is>
       </c>
       <c r="C35" s="13" t="inlineStr">
         <is>
-          <t>Админка для правок без разработчика</t>
+          <t>Публикация</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
@@ -1957,10 +1917,10 @@
         </is>
       </c>
       <c r="E35" s="9" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G35" s="14">
         <f>$B$2+E35</f>
@@ -1975,93 +1935,217 @@
           <t>Не начато</t>
         </is>
       </c>
-      <c r="J35" s="13" t="inlineStr">
-        <is>
-          <t>Отдельная задача: сайт статический</t>
+      <c r="J35" s="13" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>5. Потом, не срочно</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>Проверка переводов носителями</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Подрядчик</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F36" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G36" s="10">
+        <f>$B$2+E36</f>
+        <v/>
+      </c>
+      <c r="H36" s="10">
+        <f>G36+F36-1</f>
+        <v/>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="J36" s="8" t="inlineStr">
+        <is>
+          <t>Сайт может работать и до этого</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="15" t="inlineStr">
+      <c r="A37" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>5. Потом, не срочно</t>
+        </is>
+      </c>
+      <c r="C37" s="13" t="inlineStr">
+        <is>
+          <t>Видео с объекта</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>Заказчик</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F37" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G37" s="14">
+        <f>$B$2+E37</f>
+        <v/>
+      </c>
+      <c r="H37" s="14">
+        <f>G37+F37-1</f>
+        <v/>
+      </c>
+      <c r="I37" s="11" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="J37" s="13" t="inlineStr">
+        <is>
+          <t>Самое сильное, чего нет у конкурентов</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>5. Потом, не срочно</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="inlineStr">
+        <is>
+          <t>Админка для правок без разработчика</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>Разработка</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F38" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G38" s="14">
+        <f>$B$2+E38</f>
+        <v/>
+      </c>
+      <c r="H38" s="14">
+        <f>G38+F38-1</f>
+        <v/>
+      </c>
+      <c r="I38" s="11" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="J38" s="13" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="15" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="16" t="inlineStr">
-        <is>
-          <t>Срок проекта, дней</t>
-        </is>
-      </c>
-      <c r="C38" s="17">
-        <f>MAX(H5:H35)-$B$2+1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="16" t="inlineStr">
-        <is>
-          <t>Дата завершения</t>
-        </is>
-      </c>
-      <c r="C39" s="18">
-        <f>MAX(H5:H35)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="16" t="inlineStr">
-        <is>
-          <t>Задач всего</t>
-        </is>
-      </c>
-      <c r="C40" s="17">
-        <f>COUNTA(C5:C35)</f>
-        <v/>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="16" t="inlineStr">
         <is>
-          <t>Готово</t>
+          <t>Срок проекта, дней</t>
         </is>
       </c>
       <c r="C41" s="17">
-        <f>COUNTIF(I5:I35,"Готово")</f>
+        <f>MAX(H5:H38)-$B$2+1</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>В работе</t>
-        </is>
-      </c>
-      <c r="C42" s="17">
-        <f>COUNTIF(I5:I35,"В работе")</f>
+          <t>Дата завершения</t>
+        </is>
+      </c>
+      <c r="C42" s="18">
+        <f>MAX(H5:H38)</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="16" t="inlineStr">
         <is>
-          <t>Ждёт данных от заказчика</t>
+          <t>Задач всего</t>
         </is>
       </c>
       <c r="C43" s="17">
-        <f>COUNTIF(I5:I35,"Ждёт данных")</f>
+        <f>COUNTA(C5:C38)</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="16" t="inlineStr">
         <is>
+          <t>Готово</t>
+        </is>
+      </c>
+      <c r="C44" s="17">
+        <f>COUNTIF(I5:I38,"Готово")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="16" t="inlineStr">
+        <is>
+          <t>В работе</t>
+        </is>
+      </c>
+      <c r="C45" s="17">
+        <f>COUNTIF(I5:I38,"В работе")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="16" t="inlineStr">
+        <is>
+          <t>Ждёт данных от заказчика</t>
+        </is>
+      </c>
+      <c r="C46" s="17">
+        <f>COUNTIF(I5:I38,"Ждёт данных")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="16" t="inlineStr">
+        <is>
           <t>Не начато</t>
         </is>
       </c>
-      <c r="C44" s="17">
-        <f>COUNTIF(I5:I35,"Не начато")</f>
+      <c r="C47" s="17">
+        <f>COUNTIF(I5:I38,"Не начато")</f>
         <v/>
       </c>
     </row>
